--- a/QCM7_SVT.xlsx
+++ b/QCM7_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247BEFA2-5D16-4D26-BA7D-335504796FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D41622F-9040-406B-BF61-847A00561394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="380">
   <si>
     <t>Question</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>Explication</t>
-  </si>
-  <si>
-    <t>QCM Chapitre 5</t>
   </si>
   <si>
     <t>QCM Chapitre 7</t>
@@ -1630,25 +1627,25 @@
         <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1656,25 +1653,25 @@
         <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>93</v>
-      </c>
       <c r="H3" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1682,25 +1679,25 @@
         <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1708,25 +1705,25 @@
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>101</v>
-      </c>
       <c r="H5" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1734,25 +1731,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="H6" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1760,1863 +1757,1863 @@
         <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="H7" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="H8" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>117</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>121</v>
-      </c>
       <c r="H10" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="H11" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="H12" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>133</v>
-      </c>
       <c r="H13" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="H14" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>141</v>
-      </c>
       <c r="H15" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="H16" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="H17" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="H18" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>157</v>
-      </c>
       <c r="H19" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="H20" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>165</v>
-      </c>
       <c r="H21" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="F22" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="H24" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>178</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="H26" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>185</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>192</v>
-      </c>
       <c r="H29" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="F30" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>199</v>
-      </c>
       <c r="H31" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="F32" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>202</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="F33" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="H33" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="F34" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>210</v>
-      </c>
       <c r="H34" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="F35" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="G35" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>214</v>
-      </c>
       <c r="H35" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="F36" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="G36" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>218</v>
-      </c>
       <c r="H36" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="F37" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>221</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="F38" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>224</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="F39" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>228</v>
-      </c>
       <c r="H39" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="F40" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="G40" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>232</v>
-      </c>
       <c r="H40" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="F41" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>235</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="F42" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="F43" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="G43" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>242</v>
-      </c>
       <c r="H43" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="F44" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>245</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>248</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="F46" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="F47" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>254</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="F48" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>257</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="F49" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="G49" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>261</v>
-      </c>
       <c r="H49" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="F50" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="G50" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>265</v>
-      </c>
       <c r="H50" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="F51" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>268</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="F52" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="G52" s="4" t="s">
-        <v>272</v>
-      </c>
       <c r="H52" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="F53" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="G53" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>276</v>
-      </c>
       <c r="H53" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="G54" s="4" t="s">
-        <v>280</v>
-      </c>
       <c r="H54" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="F55" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="G55" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>284</v>
-      </c>
       <c r="H55" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="F56" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="G56" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="G56" s="4" t="s">
-        <v>288</v>
-      </c>
       <c r="H56" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="F57" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="G57" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>292</v>
-      </c>
       <c r="H57" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="F58" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="G58" s="4" t="s">
-        <v>296</v>
-      </c>
       <c r="H58" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="F59" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="G59" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>300</v>
-      </c>
       <c r="H59" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="F60" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="G60" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="G60" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="H60" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="F61" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="G61" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>308</v>
-      </c>
       <c r="H61" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="F62" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="G62" s="4" t="s">
-        <v>312</v>
-      </c>
       <c r="H62" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="F63" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="G63" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>316</v>
-      </c>
       <c r="H63" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E64" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="F64" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="G64" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="G64" s="4" t="s">
-        <v>320</v>
-      </c>
       <c r="H64" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="E65" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="F65" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="G65" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>324</v>
-      </c>
       <c r="H65" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="E66" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="F66" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="G66" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="G66" s="4" t="s">
-        <v>328</v>
-      </c>
       <c r="H66" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="E67" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="F67" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="G67" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>332</v>
-      </c>
       <c r="H67" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E68" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="F68" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="G68" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="G68" s="4" t="s">
-        <v>336</v>
-      </c>
       <c r="H68" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="F69" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="G69" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="G69" s="5" t="s">
-        <v>340</v>
-      </c>
       <c r="H69" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E70" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="F70" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="G70" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="G70" s="4" t="s">
-        <v>344</v>
-      </c>
       <c r="H70" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="F71" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="G71" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="G71" s="5" t="s">
-        <v>348</v>
-      </c>
       <c r="H71" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="E72" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="F72" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="G72" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="G72" s="4" t="s">
-        <v>352</v>
-      </c>
       <c r="H72" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E73" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="F73" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="G73" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>356</v>
-      </c>
       <c r="H73" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E74" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="F74" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="G74" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="G74" s="4" t="s">
-        <v>360</v>
-      </c>
       <c r="H74" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E75" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="F75" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="G75" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>364</v>
-      </c>
       <c r="H75" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="E76" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="F76" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="G76" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="G76" s="4" t="s">
-        <v>368</v>
-      </c>
       <c r="H76" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="F77" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="G77" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="G77" s="5" t="s">
-        <v>372</v>
-      </c>
       <c r="H77" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="E78" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="F78" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="G78" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="G78" s="4" t="s">
-        <v>376</v>
-      </c>
       <c r="H78" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="E79" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="F79" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="G79" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="G79" s="5" t="s">
-        <v>380</v>
-      </c>
       <c r="H79" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>

--- a/QCM7_SVT.xlsx
+++ b/QCM7_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D41622F-9040-406B-BF61-847A00561394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71D38AA-0100-475D-BBBB-B89B83290DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="381">
   <si>
     <t>Question</t>
   </si>
@@ -1165,6 +1165,9 @@
   </si>
   <si>
     <t>Du récepteur T et du marqueur CD8 avec le déterminant antigénique et le CMH II.</t>
+  </si>
+  <si>
+    <t>Image</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1278,6 +1281,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1582,18 +1591,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="30.42578125" customWidth="1"/>
     <col min="4" max="7" width="35" customWidth="1"/>
-    <col min="8" max="8" width="33.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="8" max="9" width="33.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1619,10 +1628,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1647,8 +1659,9 @@
       <c r="H2" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1673,8 +1686,9 @@
       <c r="H3" s="5" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1699,8 +1713,9 @@
       <c r="H4" s="4" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1725,8 +1740,9 @@
       <c r="H5" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1751,8 +1767,9 @@
       <c r="H6" s="4" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1777,8 +1794,9 @@
       <c r="H7" s="5" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1803,8 +1821,9 @@
       <c r="H8" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1829,8 +1848,9 @@
       <c r="H9" s="5" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1855,8 +1875,9 @@
       <c r="H10" s="4" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1881,8 +1902,9 @@
       <c r="H11" s="5" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1907,8 +1929,9 @@
       <c r="H12" s="4" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1933,8 +1956,9 @@
       <c r="H13" s="5" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1959,8 +1983,9 @@
       <c r="H14" s="4" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="6"/>
+    </row>
+    <row r="15" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1985,8 +2010,9 @@
       <c r="H15" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -2011,8 +2037,9 @@
       <c r="H16" s="4" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="6"/>
+    </row>
+    <row r="17" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>10</v>
       </c>
@@ -2037,8 +2064,9 @@
       <c r="H17" s="5" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
@@ -2063,8 +2091,9 @@
       <c r="H18" s="4" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="6"/>
+    </row>
+    <row r="19" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>10</v>
       </c>
@@ -2089,8 +2118,9 @@
       <c r="H19" s="5" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -2115,8 +2145,9 @@
       <c r="H20" s="4" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -2141,8 +2172,9 @@
       <c r="H21" s="5" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -2165,8 +2197,9 @@
       <c r="H22" s="4" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -2189,8 +2222,9 @@
       <c r="H23" s="5" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
@@ -2215,8 +2249,9 @@
       <c r="H24" s="4" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
@@ -2239,8 +2274,9 @@
       <c r="H25" s="5" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
@@ -2265,8 +2301,9 @@
       <c r="H26" s="4" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
@@ -2289,8 +2326,9 @@
       <c r="H27" s="5" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I27" s="7"/>
+    </row>
+    <row r="28" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>10</v>
       </c>
@@ -2313,8 +2351,9 @@
       <c r="H28" s="4" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I28" s="6"/>
+    </row>
+    <row r="29" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>10</v>
       </c>
@@ -2339,8 +2378,9 @@
       <c r="H29" s="5" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>10</v>
       </c>
@@ -2363,8 +2403,9 @@
       <c r="H30" s="4" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I30" s="6"/>
+    </row>
+    <row r="31" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>10</v>
       </c>
@@ -2389,8 +2430,9 @@
       <c r="H31" s="5" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>10</v>
       </c>
@@ -2413,8 +2455,9 @@
       <c r="H32" s="4" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I32" s="6"/>
+    </row>
+    <row r="33" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>10</v>
       </c>
@@ -2439,8 +2482,9 @@
       <c r="H33" s="5" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>10</v>
       </c>
@@ -2465,8 +2509,9 @@
       <c r="H34" s="4" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I34" s="6"/>
+    </row>
+    <row r="35" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -2491,8 +2536,9 @@
       <c r="H35" s="5" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>10</v>
       </c>
@@ -2517,8 +2563,9 @@
       <c r="H36" s="4" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I36" s="6"/>
+    </row>
+    <row r="37" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>10</v>
       </c>
@@ -2541,8 +2588,9 @@
       <c r="H37" s="5" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>10</v>
       </c>
@@ -2565,8 +2613,9 @@
       <c r="H38" s="4" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I38" s="6"/>
+    </row>
+    <row r="39" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -2591,8 +2640,9 @@
       <c r="H39" s="5" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>10</v>
       </c>
@@ -2617,8 +2667,9 @@
       <c r="H40" s="4" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I40" s="6"/>
+    </row>
+    <row r="41" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>10</v>
       </c>
@@ -2641,8 +2692,9 @@
       <c r="H41" s="5" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I41" s="7"/>
+    </row>
+    <row r="42" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -2665,8 +2717,9 @@
       <c r="H42" s="4" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I42" s="6"/>
+    </row>
+    <row r="43" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -2691,8 +2744,9 @@
       <c r="H43" s="5" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>10</v>
       </c>
@@ -2715,8 +2769,9 @@
       <c r="H44" s="4" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I44" s="6"/>
+    </row>
+    <row r="45" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -2739,8 +2794,9 @@
       <c r="H45" s="5" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>10</v>
       </c>
@@ -2763,8 +2819,9 @@
       <c r="H46" s="4" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I46" s="6"/>
+    </row>
+    <row r="47" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>10</v>
       </c>
@@ -2787,8 +2844,9 @@
       <c r="H47" s="5" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>10</v>
       </c>
@@ -2811,8 +2869,9 @@
       <c r="H48" s="4" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I48" s="6"/>
+    </row>
+    <row r="49" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>10</v>
       </c>
@@ -2837,8 +2896,9 @@
       <c r="H49" s="5" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>10</v>
       </c>
@@ -2863,8 +2923,9 @@
       <c r="H50" s="4" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I50" s="6"/>
+    </row>
+    <row r="51" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>10</v>
       </c>
@@ -2887,8 +2948,9 @@
       <c r="H51" s="5" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I51" s="7"/>
+    </row>
+    <row r="52" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>10</v>
       </c>
@@ -2913,8 +2975,9 @@
       <c r="H52" s="4" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I52" s="6"/>
+    </row>
+    <row r="53" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>10</v>
       </c>
@@ -2939,8 +3002,9 @@
       <c r="H53" s="5" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I53" s="7"/>
+    </row>
+    <row r="54" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>10</v>
       </c>
@@ -2965,8 +3029,9 @@
       <c r="H54" s="4" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I54" s="6"/>
+    </row>
+    <row r="55" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>10</v>
       </c>
@@ -2991,8 +3056,9 @@
       <c r="H55" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>10</v>
       </c>
@@ -3017,8 +3083,9 @@
       <c r="H56" s="4" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I56" s="6"/>
+    </row>
+    <row r="57" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>10</v>
       </c>
@@ -3043,8 +3110,9 @@
       <c r="H57" s="5" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>10</v>
       </c>
@@ -3069,8 +3137,9 @@
       <c r="H58" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I58" s="6"/>
+    </row>
+    <row r="59" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>10</v>
       </c>
@@ -3095,8 +3164,9 @@
       <c r="H59" s="5" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I59" s="7"/>
+    </row>
+    <row r="60" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>10</v>
       </c>
@@ -3121,8 +3191,9 @@
       <c r="H60" s="4" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I60" s="6"/>
+    </row>
+    <row r="61" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>10</v>
       </c>
@@ -3147,8 +3218,9 @@
       <c r="H61" s="5" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>10</v>
       </c>
@@ -3173,8 +3245,9 @@
       <c r="H62" s="4" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I62" s="6"/>
+    </row>
+    <row r="63" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -3199,8 +3272,9 @@
       <c r="H63" s="5" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>10</v>
       </c>
@@ -3225,8 +3299,9 @@
       <c r="H64" s="4" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I64" s="6"/>
+    </row>
+    <row r="65" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>10</v>
       </c>
@@ -3251,8 +3326,9 @@
       <c r="H65" s="5" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I65" s="7"/>
+    </row>
+    <row r="66" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>10</v>
       </c>
@@ -3277,8 +3353,9 @@
       <c r="H66" s="4" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I66" s="6"/>
+    </row>
+    <row r="67" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>10</v>
       </c>
@@ -3303,8 +3380,9 @@
       <c r="H67" s="5" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I67" s="7"/>
+    </row>
+    <row r="68" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>10</v>
       </c>
@@ -3329,8 +3407,9 @@
       <c r="H68" s="4" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I68" s="6"/>
+    </row>
+    <row r="69" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>10</v>
       </c>
@@ -3355,8 +3434,9 @@
       <c r="H69" s="5" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I69" s="7"/>
+    </row>
+    <row r="70" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>10</v>
       </c>
@@ -3381,8 +3461,9 @@
       <c r="H70" s="4" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I70" s="6"/>
+    </row>
+    <row r="71" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>10</v>
       </c>
@@ -3407,8 +3488,9 @@
       <c r="H71" s="5" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I71" s="7"/>
+    </row>
+    <row r="72" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>10</v>
       </c>
@@ -3433,8 +3515,9 @@
       <c r="H72" s="4" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I72" s="6"/>
+    </row>
+    <row r="73" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>10</v>
       </c>
@@ -3459,8 +3542,9 @@
       <c r="H73" s="5" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I73" s="7"/>
+    </row>
+    <row r="74" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>10</v>
       </c>
@@ -3485,8 +3569,9 @@
       <c r="H74" s="4" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I74" s="6"/>
+    </row>
+    <row r="75" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>10</v>
       </c>
@@ -3511,8 +3596,9 @@
       <c r="H75" s="5" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I75" s="7"/>
+    </row>
+    <row r="76" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>10</v>
       </c>
@@ -3537,8 +3623,9 @@
       <c r="H76" s="4" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I76" s="6"/>
+    </row>
+    <row r="77" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>10</v>
       </c>
@@ -3563,8 +3650,9 @@
       <c r="H77" s="5" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I77" s="7"/>
+    </row>
+    <row r="78" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>10</v>
       </c>
@@ -3589,8 +3677,9 @@
       <c r="H78" s="4" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I78" s="6"/>
+    </row>
+    <row r="79" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>10</v>
       </c>
@@ -3615,6 +3704,7 @@
       <c r="H79" s="5" t="s">
         <v>377</v>
       </c>
+      <c r="I79" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/QCM7_SVT.xlsx
+++ b/QCM7_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71D38AA-0100-475D-BBBB-B89B83290DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6ED1D9-567A-4A42-BC3F-560DBEA65A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,9 +57,6 @@
     <t>Explication</t>
   </si>
   <si>
-    <t>QCM Chapitre 7</t>
-  </si>
-  <si>
     <t>Le complexe majeur de l'histocompatibilité est :</t>
   </si>
   <si>
@@ -1168,6 +1165,9 @@
   </si>
   <si>
     <t>Image</t>
+  </si>
+  <si>
+    <t>TEST : L'immunité</t>
   </si>
 </sst>
 </file>
@@ -1628,7 +1628,7 @@
         <v>8</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>9</v>
@@ -1636,2073 +1636,2073 @@
     </row>
     <row r="2" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>92</v>
-      </c>
       <c r="H3" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="H5" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="H6" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="H7" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I7" s="7"/>
     </row>
     <row r="8" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>112</v>
-      </c>
       <c r="H8" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>116</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="H10" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="H11" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>128</v>
-      </c>
       <c r="H12" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>132</v>
-      </c>
       <c r="H13" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="H14" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>140</v>
-      </c>
       <c r="H15" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="H16" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>148</v>
-      </c>
       <c r="H17" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="H18" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>156</v>
-      </c>
       <c r="H19" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="H20" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I20" s="6"/>
     </row>
     <row r="21" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>164</v>
-      </c>
       <c r="H21" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="F22" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I22" s="6"/>
     </row>
     <row r="23" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>170</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="H24" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I24" s="6"/>
     </row>
     <row r="25" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>177</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>181</v>
-      </c>
       <c r="H26" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I26" s="6"/>
     </row>
     <row r="27" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>184</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>187</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I28" s="6"/>
     </row>
     <row r="29" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>191</v>
-      </c>
       <c r="H29" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="F30" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>194</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I30" s="6"/>
     </row>
     <row r="31" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>198</v>
-      </c>
       <c r="H31" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="F32" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>201</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I32" s="6"/>
     </row>
     <row r="33" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="F33" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>205</v>
-      </c>
       <c r="H33" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I33" s="7"/>
     </row>
     <row r="34" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="F34" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="H34" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I34" s="6"/>
     </row>
     <row r="35" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="F35" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="G35" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>213</v>
-      </c>
       <c r="H35" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="F36" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="G36" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>217</v>
-      </c>
       <c r="H36" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I36" s="6"/>
     </row>
     <row r="37" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="F37" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="F38" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I38" s="6"/>
     </row>
     <row r="39" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="F39" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>227</v>
-      </c>
       <c r="H39" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="F40" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="G40" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>231</v>
-      </c>
       <c r="H40" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I40" s="6"/>
     </row>
     <row r="41" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="F41" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I41" s="7"/>
     </row>
     <row r="42" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="F42" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>237</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I42" s="6"/>
     </row>
     <row r="43" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="F43" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="G43" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="H43" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="F44" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I44" s="6"/>
     </row>
     <row r="45" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>246</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>247</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I45" s="7"/>
     </row>
     <row r="46" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="F46" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>250</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I46" s="6"/>
     </row>
     <row r="47" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="F47" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>253</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="F48" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I48" s="6"/>
     </row>
     <row r="49" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="F49" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="G49" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>260</v>
-      </c>
       <c r="H49" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I49" s="7"/>
     </row>
     <row r="50" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="F50" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="G50" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>264</v>
-      </c>
       <c r="H50" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I50" s="6"/>
     </row>
     <row r="51" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="F51" s="5" t="s">
         <v>266</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>267</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I51" s="7"/>
     </row>
     <row r="52" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="F52" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="G52" s="4" t="s">
-        <v>271</v>
-      </c>
       <c r="H52" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I52" s="6"/>
     </row>
     <row r="53" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="F53" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="G53" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>275</v>
-      </c>
       <c r="H53" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I53" s="7"/>
     </row>
     <row r="54" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="G54" s="4" t="s">
-        <v>279</v>
-      </c>
       <c r="H54" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I54" s="6"/>
     </row>
     <row r="55" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="F55" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="G55" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>283</v>
-      </c>
       <c r="H55" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I55" s="7"/>
     </row>
     <row r="56" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="F56" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="G56" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="G56" s="4" t="s">
-        <v>287</v>
-      </c>
       <c r="H56" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I56" s="6"/>
     </row>
     <row r="57" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="F57" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="G57" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>291</v>
-      </c>
       <c r="H57" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I57" s="7"/>
     </row>
     <row r="58" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="F58" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="G58" s="4" t="s">
-        <v>295</v>
-      </c>
       <c r="H58" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I58" s="6"/>
     </row>
     <row r="59" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="F59" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="G59" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>299</v>
-      </c>
       <c r="H59" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I59" s="7"/>
     </row>
     <row r="60" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="F60" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="G60" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="G60" s="4" t="s">
-        <v>303</v>
-      </c>
       <c r="H60" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I60" s="6"/>
     </row>
     <row r="61" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="F61" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="G61" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>307</v>
-      </c>
       <c r="H61" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I61" s="7"/>
     </row>
     <row r="62" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="F62" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="G62" s="4" t="s">
-        <v>311</v>
-      </c>
       <c r="H62" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I62" s="6"/>
     </row>
     <row r="63" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="F63" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="G63" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>315</v>
-      </c>
       <c r="H63" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I63" s="7"/>
     </row>
     <row r="64" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="E64" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="F64" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="G64" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="G64" s="4" t="s">
-        <v>319</v>
-      </c>
       <c r="H64" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I64" s="6"/>
     </row>
     <row r="65" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="E65" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="F65" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="G65" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>323</v>
-      </c>
       <c r="H65" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I65" s="7"/>
     </row>
     <row r="66" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E66" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="F66" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="G66" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="G66" s="4" t="s">
-        <v>327</v>
-      </c>
       <c r="H66" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I66" s="6"/>
     </row>
     <row r="67" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="E67" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="F67" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="G67" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>331</v>
-      </c>
       <c r="H67" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I67" s="7"/>
     </row>
     <row r="68" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="E68" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="F68" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="G68" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="G68" s="4" t="s">
-        <v>335</v>
-      </c>
       <c r="H68" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I68" s="6"/>
     </row>
     <row r="69" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="F69" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="G69" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="G69" s="5" t="s">
-        <v>339</v>
-      </c>
       <c r="H69" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I69" s="7"/>
     </row>
     <row r="70" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="E70" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="F70" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="G70" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="G70" s="4" t="s">
-        <v>343</v>
-      </c>
       <c r="H70" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I70" s="6"/>
     </row>
     <row r="71" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="F71" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="G71" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="G71" s="5" t="s">
-        <v>347</v>
-      </c>
       <c r="H71" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I71" s="7"/>
     </row>
     <row r="72" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="E72" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="F72" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="G72" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="G72" s="4" t="s">
-        <v>351</v>
-      </c>
       <c r="H72" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I72" s="6"/>
     </row>
     <row r="73" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E73" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="F73" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="G73" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>355</v>
-      </c>
       <c r="H73" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I73" s="7"/>
     </row>
     <row r="74" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="E74" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="F74" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="G74" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="G74" s="4" t="s">
-        <v>359</v>
-      </c>
       <c r="H74" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I74" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E75" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="F75" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="G75" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>363</v>
-      </c>
       <c r="H75" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I75" s="7"/>
     </row>
     <row r="76" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="E76" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="F76" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="G76" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="G76" s="4" t="s">
-        <v>367</v>
-      </c>
       <c r="H76" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I76" s="6"/>
     </row>
     <row r="77" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="F77" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="G77" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="G77" s="5" t="s">
-        <v>371</v>
-      </c>
       <c r="H77" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I77" s="7"/>
     </row>
     <row r="78" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="E78" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="F78" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="G78" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="G78" s="4" t="s">
-        <v>375</v>
-      </c>
       <c r="H78" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I78" s="6"/>
     </row>
     <row r="79" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="E79" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="F79" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="G79" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="G79" s="5" t="s">
-        <v>379</v>
-      </c>
       <c r="H79" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I79" s="7"/>
     </row>
